--- a/AfterToken/Configs/GameConfig/Datas/level.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/level.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,11 @@
           <t>rewardExp</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>extractionTime</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,6 +554,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,29 +626,34 @@
           <t>通关奖励经验</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>撤离倒计时秒数</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Training Ground L1</t>
+          <t>3D Training Ground L1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BattleScene_L01</t>
+          <t>BattleScene_3D_L01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>First battle scene with portal to L2.</t>
+          <t>First 3D battle scene.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1001,1002,1003</t>
+          <t>1001,1003,1004,1005</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -648,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
         <v>9001</v>
@@ -661,25 +676,28 @@
       </c>
       <c r="M4" t="n">
         <v>50</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Abandoned Factory L2</t>
+          <t>3D Abandoned Factory L2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BattleScene_L02</t>
+          <t>BattleScene_3D_L02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Second battle scene with portal to L3.</t>
+          <t>Second 3D battle scene.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -694,7 +712,7 @@
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
         <v>9001</v>
@@ -707,25 +725,28 @@
       </c>
       <c r="M5" t="n">
         <v>80</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boss Arena L3</t>
+          <t>3D Boss Arena L3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BattleScene_L03</t>
+          <t>BattleScene_3D_L03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Final battle scene with return portal.</t>
+          <t>Final 3D battle scene.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -740,7 +761,7 @@
         <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J6" t="n">
         <v>9001</v>
@@ -754,143 +775,8 @@
       <c r="M6" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3D Training Ground L1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>BattleScene_3D_L01</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>First 3D battle scene.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1001,1003,1004</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>100</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="N6" t="n">
         <v>10</v>
-      </c>
-      <c r="I7" t="n">
-        <v>12</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9001</v>
-      </c>
-      <c r="K7" t="n">
-        <v>50</v>
-      </c>
-      <c r="L7" t="n">
-        <v>100</v>
-      </c>
-      <c r="M7" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>102</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3D Abandoned Factory L2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BattleScene_3D_L02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Second 3D battle scene.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1002,1003,1004</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" t="n">
-        <v>9001</v>
-      </c>
-      <c r="K8" t="n">
-        <v>80</v>
-      </c>
-      <c r="L8" t="n">
-        <v>150</v>
-      </c>
-      <c r="M8" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="n">
-        <v>103</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3D Boss Arena L3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>BattleScene_3D_L03</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Final 3D battle scene.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1002,1003,1004</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H9" t="n">
-        <v>20</v>
-      </c>
-      <c r="I9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9001</v>
-      </c>
-      <c r="K9" t="n">
-        <v>100</v>
-      </c>
-      <c r="L9" t="n">
-        <v>300</v>
-      </c>
-      <c r="M9" t="n">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
